--- a/src/flychams_common/config/Configuration-Assignment-Benchmark.xlsx
+++ b/src/flychams_common/config/Configuration-Assignment-Benchmark.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -100,25 +100,7 @@
     <t xml:space="preserve">MISSION01</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3 Multi-Window Agents Configuration</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (2 Windows)</t>
-    </r>
+    <t xml:space="preserve">3 Multi-Window Agents Configuration (2 Windows)</t>
   </si>
   <si>
     <t xml:space="preserve">TEAM01</t>
@@ -127,25 +109,7 @@
     <t xml:space="preserve">MISSION02</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2 Multi-Window Agents Configuration</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (4 Windows)</t>
-    </r>
+    <t xml:space="preserve">2 Multi-Window Agents Configuration (4 Windows)</t>
   </si>
   <si>
     <t xml:space="preserve">TEAM02</t>
@@ -154,25 +118,7 @@
     <t xml:space="preserve">MISSION03</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4 Multi-Window Agents Configuration</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (2 Windows)</t>
-    </r>
+    <t xml:space="preserve">4 Multi-Window Agents Configuration (2 Windows)</t>
   </si>
   <si>
     <t xml:space="preserve">TEAM03</t>
@@ -935,7 +881,7 @@
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1010,12 +956,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1109,7 +1049,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1160,10 +1100,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1829,11 +1765,9 @@
       <c r="BB3" s="12"/>
       <c r="BC3" s="12"/>
       <c r="BD3" s="12"/>
-      <c r="XFC3" s="0"/>
-      <c r="XFD3" s="0"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13"/>
+      <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
         <v>22</v>
       </c>
@@ -1911,7 +1845,7 @@
       <c r="BD4" s="12"/>
     </row>
     <row r="5" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13"/>
+      <c r="A5" s="8"/>
       <c r="B5" s="9" t="s">
         <v>25</v>
       </c>
@@ -1987,11 +1921,9 @@
       <c r="BB5" s="12"/>
       <c r="BC5" s="12"/>
       <c r="BD5" s="12"/>
-      <c r="XFC5" s="0"/>
-      <c r="XFD5" s="0"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13"/>
+      <c r="A6" s="8"/>
       <c r="B6" s="9" t="s">
         <v>28</v>
       </c>
@@ -2067,8 +1999,6 @@
       <c r="BB6" s="12"/>
       <c r="BC6" s="12"/>
       <c r="BD6" s="12"/>
-      <c r="XFC6" s="0"/>
-      <c r="XFD6" s="0"/>
     </row>
     <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2114,92 +2044,92 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>255</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>276</v>
       </c>
-      <c r="C3" s="23" t="b">
+      <c r="C3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="E3" s="23" t="b">
+      <c r="E3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="G3" s="23" t="b">
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="I3" s="22" t="n">
+      <c r="I3" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="J3" s="22" t="n">
+      <c r="J3" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="22" t="n">
+      <c r="K3" s="21" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2253,12 +2183,12 @@
   </cols>
   <sheetData>
     <row r="1" s="7" customFormat="true" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
       <c r="E1" s="12"/>
       <c r="XFB1" s="3"/>
       <c r="XFC1" s="3"/>
@@ -2288,7 +2218,7 @@
       <c r="C3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2302,7 +2232,7 @@
       <c r="C4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2342,15 +2272,15 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -2446,7 +2376,7 @@
       <c r="D3" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="15" t="n">
         <v>16</v>
       </c>
       <c r="F3" s="9" t="s">
@@ -2562,48 +2492,48 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>55</v>
       </c>
       <c r="L2" s="12"/>
@@ -2618,361 +2548,356 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H3" s="19" t="n">
+      <c r="H3" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H4" s="19" t="n">
+      <c r="H4" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="I6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I7" s="19" t="n">
+      <c r="I7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="I8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J8" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="XFD9" s="0"/>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="XFD10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="XFD11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I12" s="19" t="n">
+      <c r="I12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J12" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="XFD12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H13" s="19" t="n">
+      <c r="H13" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I13" s="19" t="n">
+      <c r="I13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="19" t="n">
+      <c r="J13" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="XFD13" s="0"/>
     </row>
     <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3021,32 +2946,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>98</v>
       </c>
       <c r="H2" s="12"/>
@@ -3062,22 +2987,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="19" t="n">
+      <c r="D3" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E3" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -3087,22 +3012,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -3112,22 +3037,22 @@
       <c r="XEY4" s="3"/>
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G5" s="2"/>
@@ -3137,22 +3062,22 @@
       <c r="XEY5" s="3"/>
     </row>
     <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G6" s="2"/>
@@ -3162,22 +3087,22 @@
       <c r="XEY6" s="3"/>
     </row>
     <row r="7" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G7" s="2"/>
@@ -3187,22 +3112,22 @@
       <c r="XEY7" s="3"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G8" s="2"/>
@@ -3212,22 +3137,22 @@
       <c r="XEY8" s="3"/>
     </row>
     <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G9" s="2"/>
@@ -3237,22 +3162,22 @@
       <c r="XEY9" s="3"/>
     </row>
     <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" s="2"/>
@@ -3262,22 +3187,22 @@
       <c r="XEY10" s="3"/>
     </row>
     <row r="11" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G11" s="2"/>
@@ -3287,22 +3212,22 @@
       <c r="XEY11" s="3"/>
     </row>
     <row r="12" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G12" s="2"/>
@@ -3312,22 +3237,22 @@
       <c r="XEY12" s="3"/>
     </row>
     <row r="13" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G13" s="2"/>
@@ -3390,56 +3315,56 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="17" t="s">
         <v>127</v>
       </c>
       <c r="M2" s="12"/>
@@ -3452,427 +3377,427 @@
       <c r="XFC2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="19" t="n">
+      <c r="K3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="19" t="s">
+      <c r="L3" s="18" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K4" s="19" t="n">
+      <c r="K4" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="L4" s="18" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="K5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="L5" s="18" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="I6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="19" t="n">
+      <c r="K6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="18" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I7" s="19" t="n">
+      <c r="I7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="19" t="n">
+      <c r="K7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" s="18" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="I8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="19" t="n">
+      <c r="K8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L8" s="18" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="19" t="n">
+      <c r="K9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L9" s="19" t="s">
+      <c r="L9" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="XFD9" s="0"/>
+      <c r="XFD9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K10" s="19" t="n">
+      <c r="K10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="XFD10" s="0"/>
+      <c r="XFD10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="19" t="n">
+      <c r="K11" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L11" s="19" t="s">
+      <c r="L11" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="XFD11" s="0"/>
+      <c r="XFD11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="H12" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I12" s="19" t="n">
+      <c r="I12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K12" s="19" t="n">
+      <c r="K12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L12" s="19" t="s">
+      <c r="L12" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="XFD12" s="0"/>
+      <c r="XFD12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H13" s="19" t="s">
+      <c r="H13" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I13" s="19" t="n">
+      <c r="I13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="19" t="n">
+      <c r="J13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K13" s="19" t="n">
+      <c r="K13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L13" s="19" t="s">
+      <c r="L13" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="XFD13" s="0"/>
+      <c r="XFD13" s="3"/>
     </row>
     <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3924,36 +3849,36 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>169</v>
       </c>
       <c r="XEU2" s="3"/>
@@ -3968,652 +3893,646 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E3" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="19" t="n">
+      <c r="G3" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="19" t="n">
+      <c r="G4" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="XFD5" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="XFD8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="19" t="n">
+      <c r="G13" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G14" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G15" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G16" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E17" s="19" t="n">
+      <c r="E17" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="19" t="n">
+      <c r="G17" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="XFD17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E18" s="19" t="n">
+      <c r="E18" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G18" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="XFD18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E19" s="19" t="n">
+      <c r="E19" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="19" t="n">
+      <c r="G19" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E20" s="19" t="n">
+      <c r="E20" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G20" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E21" s="19" t="n">
+      <c r="E21" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F21" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="19" t="n">
+      <c r="G21" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="XFD21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E22" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="19" t="n">
+      <c r="G22" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="XFD22" s="0"/>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E23" s="19" t="n">
+      <c r="E23" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F23" s="19" t="n">
+      <c r="F23" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="19" t="n">
+      <c r="G23" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E24" s="19" t="n">
+      <c r="E24" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F24" s="19" t="n">
+      <c r="F24" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="19" t="n">
+      <c r="G24" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E25" s="19" t="n">
+      <c r="E25" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F25" s="19" t="n">
+      <c r="F25" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="19" t="n">
+      <c r="G25" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E26" s="19" t="n">
+      <c r="E26" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F26" s="19" t="n">
+      <c r="F26" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="19" t="n">
+      <c r="G26" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E27" s="19" t="n">
+      <c r="E27" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F27" s="19" t="n">
+      <c r="F27" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="19" t="n">
+      <c r="G27" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E28" s="19" t="n">
+      <c r="E28" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F28" s="19" t="n">
+      <c r="F28" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="19" t="n">
+      <c r="G28" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E29" s="19" t="n">
+      <c r="E29" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F29" s="19" t="n">
+      <c r="F29" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="19" t="n">
+      <c r="G29" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E30" s="19" t="n">
+      <c r="E30" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F30" s="19" t="n">
+      <c r="F30" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="19" t="n">
+      <c r="G30" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
@@ -4668,140 +4587,140 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="L2" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="N2" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="P2" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="Q2" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="R2" s="20" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>244</v>
       </c>
-      <c r="D3" s="22" t="n">
+      <c r="D3" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="22" t="n">
+      <c r="E3" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="23" t="b">
+      <c r="F3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="H3" s="23" t="b">
+      <c r="H3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="21" t="s">
         <v>246</v>
       </c>
-      <c r="J3" s="23" t="b">
+      <c r="J3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="L3" s="23" t="b">
+      <c r="L3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="M3" s="21" t="s">
         <v>248</v>
       </c>
-      <c r="N3" s="22" t="n">
+      <c r="N3" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="22" t="n">
+      <c r="O3" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="22" t="n">
+      <c r="P3" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="22" t="n">
+      <c r="Q3" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="22" t="n">
+      <c r="R3" s="21" t="n">
         <v>25</v>
       </c>
     </row>
@@ -4861,52 +4780,52 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>255</v>
       </c>
       <c r="XFB2" s="3"/>
@@ -4914,110 +4833,110 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="G3" s="23" t="b">
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="I3" s="22" t="n">
+      <c r="I3" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J3" s="22" t="n">
+      <c r="J3" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="22" t="n">
+      <c r="K3" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="G4" s="23" t="b">
+      <c r="G4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="I4" s="22" t="n">
+      <c r="I4" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="22" t="n">
+      <c r="J4" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="22" t="n">
+      <c r="K4" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="G5" s="23" t="b">
+      <c r="G5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="21" t="s">
         <v>269</v>
       </c>
-      <c r="I5" s="22" t="n">
+      <c r="I5" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="22" t="n">
+      <c r="J5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="22" t="n">
+      <c r="K5" s="21" t="n">
         <v>5</v>
       </c>
     </row>

--- a/src/flychams_common/config/Configuration-Assignment-Benchmark.xlsx
+++ b/src/flychams_common/config/Configuration-Assignment-Benchmark.xlsx
@@ -881,7 +881,7 @@
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -942,13 +942,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1082,7 +1075,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1094,7 +1087,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/src/flychams_common/config/Configuration-Assignment-Benchmark.xlsx
+++ b/src/flychams_common/config/Configuration-Assignment-Benchmark.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="279">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -64,49 +64,58 @@
     <t xml:space="preserve">StartHour</t>
   </si>
   <si>
+    <t xml:space="preserve">MISSION00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Multi-Window Agents Configuration (3 Windows)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENVIRONMENT00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GROUP00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-150.0, 150.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(30.0, 150.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PX4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(13/12/2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(16:30:00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Multi-Window Agents Configuration (2 Windows)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Multi-Window Agents Configuration (2 Windows)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM03</t>
+  </si>
+  <si>
     <t xml:space="preserve">X</t>
   </si>
   <si>
-    <t xml:space="preserve">MISSION00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Multi-Window Agents Configuration (3 Windows)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENVIRONMENT00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROUP00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(-150.0, 150.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(30.0, 150.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PX4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(13/12/2024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(16:30:00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 Multi-Window Agents Configuration (2 Windows)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION02</t>
+    <t xml:space="preserve">MISSION03</t>
   </si>
   <si>
     <t xml:space="preserve">2 Multi-Window Agents Configuration (4 Windows)</t>
@@ -115,15 +124,6 @@
     <t xml:space="preserve">TEAM02</t>
   </si>
   <si>
-    <t xml:space="preserve">MISSION03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 Multi-Window Agents Configuration (2 Windows)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM03</t>
-  </si>
-  <si>
     <t xml:space="preserve">Geopoint</t>
   </si>
   <si>
@@ -163,7 +163,7 @@
     <t xml:space="preserve">TARGET00</t>
   </si>
   <si>
-    <t xml:space="preserve">Complex Configuration (6 Clusters)</t>
+    <t xml:space="preserve">Mixed Configuration (6 Clusters)</t>
   </si>
   <si>
     <t xml:space="preserve">Human</t>
@@ -172,7 +172,7 @@
     <t xml:space="preserve">High</t>
   </si>
   <si>
-    <t xml:space="preserve">Complex</t>
+    <t xml:space="preserve">Complex-Mixed</t>
   </si>
   <si>
     <t xml:space="preserve">AGENT CONFIGURATION</t>
@@ -529,255 +529,252 @@
     <t xml:space="preserve">rtsp://127.0.0.1:8554/AGENT10/MULTICAMERA10</t>
   </si>
   <si>
+    <t xml:space="preserve">MinLambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxLambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RefLambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 1.1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 1.1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 1.1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 1.2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 1.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 1.2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 2.1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 2.1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 2.2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 2.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 2.3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 2.3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 3.1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 3.1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 3.1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 3.1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 3.2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 3.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 3.2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 3.2.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 4.1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 4.1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 4.2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 4.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 4.3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 4.3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 4.4.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Multi-Window 4.4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARDWARE CATALOGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CruiseSpeed [m/s]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxSpeed [m/s]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnableBarometer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barometer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnableIMU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnableGPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnableMagnetometer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnetometer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BaseWeight [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxPayloadWeight [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HoverPower [W]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CruisePower [W]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LoadFactor [W/kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quadcopter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(WhiteNoiseSigma=8.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(AngularWhiteNoiseSigma=0.8, VelocityWhiteNoiseSigma=0.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(EphIni=50, EpvIni=50, EphFin=2.0, EpvFin=2.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(WhiteNoiseSigma=0.02, WhiteNoiseBias=0)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resolution [pix]</t>
   </si>
   <si>
-    <t xml:space="preserve">MinLambda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxLambda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RefLambda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 1.1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(480x270)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 1.1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 1.1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 1.2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 1.2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 1.2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 2.1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 2.1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 2.2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 2.2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 2.3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 2.3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 3.1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 3.1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 3.1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 3.1.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 3.2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 3.2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 3.2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 3.2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 4.1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 4.1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 4.2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 4.2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 4.3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 4.3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 4.4.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Multi-Window 4.4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARDWARE CATALOGS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CruiseSpeed [m/s]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxSpeed [m/s]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnableBarometer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barometer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnableIMU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnableGPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnableMagnetometer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magnetometer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BaseWeight [kg]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxPayloadWeight [kg]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HoverPower [W]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CruisePower [W]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LoadFactor [W/kg]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quadcopter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(WhiteNoiseSigma=8.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(AngularWhiteNoiseSigma=0.8, VelocityWhiteNoiseSigma=0.6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(EphIni=50, EpvIni=50, EphFin=2.0, EpvFin=2.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(WhiteNoiseSigma=0.02, WhiteNoiseBias=0)</t>
-  </si>
-  <si>
     <t xml:space="preserve">SensorSize [mm]</t>
   </si>
   <si>
@@ -832,7 +829,7 @@
     <t xml:space="preserve">High-Resolution Central Camera</t>
   </si>
   <si>
-    <t xml:space="preserve">(3840x2160)</t>
+    <t xml:space="preserve">(1920x1080)</t>
   </si>
   <si>
     <t xml:space="preserve">(-0.08, 0.008, 0.0001, 0.002, -0.0015)</t>
@@ -881,7 +878,7 @@
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -949,6 +946,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1042,7 +1046,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1095,6 +1099,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1103,7 +1111,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1318,16 +1326,15 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table210_2" displayName="Table210_2" ref="A2:G4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A2:G4"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table210_2" displayName="Table210_2" ref="A2:F4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A2:F4"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Name"/>
     <tableColumn id="3" name="ObservationSetID"/>
-    <tableColumn id="4" name="Resolution [pix]"/>
-    <tableColumn id="5" name="MinLambda"/>
-    <tableColumn id="6" name="MaxLambda"/>
-    <tableColumn id="7" name="RefLambda"/>
+    <tableColumn id="4" name="MinLambda"/>
+    <tableColumn id="5" name="MaxLambda"/>
+    <tableColumn id="6" name="RefLambda"/>
   </tableColumns>
 </table>
 </file>
@@ -1680,38 +1687,36 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="J3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
@@ -1762,34 +1767,34 @@
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>24</v>
-      </c>
       <c r="G4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="K4" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
@@ -1840,34 +1845,34 @@
     <row r="5" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8"/>
       <c r="B5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="G5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="I5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="J5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="K5" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
@@ -1916,7 +1921,9 @@
       <c r="BD5" s="12"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8"/>
+      <c r="A6" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="B6" s="9" t="s">
         <v>28</v>
       </c>
@@ -1924,28 +1931,28 @@
         <v>29</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>15</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="I6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="J6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="K6" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
@@ -2037,92 +2044,92 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="20" t="s">
+      <c r="A2" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="D2" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>271</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="H2" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="J2" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>254</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>255</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3" s="23" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>276</v>
       </c>
-      <c r="C3" s="22" t="b">
+      <c r="E3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>277</v>
       </c>
-      <c r="E3" s="22" t="b">
+      <c r="G3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="H3" s="22" t="s">
         <v>278</v>
       </c>
-      <c r="G3" s="22" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="I3" s="21" t="n">
+      <c r="I3" s="22" t="n">
         <v>0.4</v>
       </c>
-      <c r="J3" s="21" t="n">
+      <c r="J3" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="21" t="n">
+      <c r="K3" s="22" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2176,12 +2183,12 @@
   </cols>
   <sheetData>
     <row r="1" s="7" customFormat="true" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
       <c r="E1" s="12"/>
       <c r="XFB1" s="3"/>
       <c r="XFC1" s="3"/>
@@ -2203,7 +2210,7 @@
     </row>
     <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>33</v>
@@ -2211,7 +2218,7 @@
       <c r="C3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2225,7 +2232,7 @@
       <c r="C4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2265,15 +2272,15 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -2356,7 +2363,7 @@
       <c r="BL2" s="7"/>
       <c r="BM2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
         <v>43</v>
       </c>
@@ -2364,13 +2371,13 @@
         <v>44</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="15" t="n">
-        <v>16</v>
+      <c r="E3" s="16" t="n">
+        <v>18</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>46</v>
@@ -2435,7 +2442,6 @@
       <c r="BJ3" s="12"/>
       <c r="BK3" s="12"/>
       <c r="BL3" s="12"/>
-      <c r="BM3" s="3"/>
     </row>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2485,48 +2491,48 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="A2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="18" t="s">
         <v>55</v>
       </c>
       <c r="L2" s="12"/>
@@ -2541,354 +2547,354 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="18" t="s">
+      <c r="C3" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H3" s="18" t="n">
+      <c r="H3" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="I3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="18" t="s">
+      <c r="C4" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="H4" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="I4" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="18" t="s">
+      <c r="C5" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="18" t="s">
+      <c r="C6" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H6" s="18" t="n">
+      <c r="H6" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J6" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="18" t="s">
+      <c r="C7" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H7" s="18" t="n">
+      <c r="H7" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="18" t="s">
+      <c r="C8" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="18" t="n">
+      <c r="H8" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="18" t="s">
+      <c r="C9" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="H9" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="18" t="s">
+      <c r="C10" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="18" t="n">
+      <c r="H10" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J10" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="18" t="s">
+      <c r="C11" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="18" t="n">
+      <c r="H11" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="J11" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="18" t="s">
+      <c r="C12" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="18" t="n">
+      <c r="J12" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="18" t="s">
+      <c r="C13" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="H13" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J13" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -2939,32 +2945,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="A2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>98</v>
       </c>
       <c r="H2" s="12"/>
@@ -2980,22 +2986,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -3005,22 +3011,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -3030,22 +3036,22 @@
       <c r="XEY4" s="3"/>
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G5" s="2"/>
@@ -3055,22 +3061,22 @@
       <c r="XEY5" s="3"/>
     </row>
     <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G6" s="2"/>
@@ -3080,22 +3086,22 @@
       <c r="XEY6" s="3"/>
     </row>
     <row r="7" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G7" s="2"/>
@@ -3105,22 +3111,22 @@
       <c r="XEY7" s="3"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G8" s="2"/>
@@ -3130,22 +3136,22 @@
       <c r="XEY8" s="3"/>
     </row>
     <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G9" s="2"/>
@@ -3155,22 +3161,22 @@
       <c r="XEY9" s="3"/>
     </row>
     <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" s="2"/>
@@ -3180,22 +3186,22 @@
       <c r="XEY10" s="3"/>
     </row>
     <row r="11" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G11" s="2"/>
@@ -3205,22 +3211,22 @@
       <c r="XEY11" s="3"/>
     </row>
     <row r="12" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G12" s="2"/>
@@ -3230,22 +3236,22 @@
       <c r="XEY12" s="3"/>
     </row>
     <row r="13" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G13" s="2"/>
@@ -3308,56 +3314,56 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="A2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="18" t="s">
         <v>127</v>
       </c>
       <c r="M2" s="12"/>
@@ -3370,427 +3376,426 @@
       <c r="XFC2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="I3" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="L3" s="19" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="I4" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="18" t="n">
+      <c r="L4" s="19" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="18" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" s="18" t="s">
+      <c r="L5" s="19" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E6" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F6" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G6" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H6" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="I6" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="L6" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K4" s="18" t="n">
+      <c r="L7" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="XFD7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="18" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" s="18" t="s">
+      <c r="L8" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="XFD8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E9" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F9" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G9" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H9" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="L9" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="XFD9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K5" s="18" t="n">
+      <c r="L10" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="XFD10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L5" s="18" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D6" s="18" t="s">
+      <c r="L11" s="19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E12" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F12" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G12" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H12" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="L12" s="19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" s="18" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="I7" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" s="18" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="I8" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" s="18" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="XFD9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="XFD10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="XFD11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="XFD12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" s="18" t="s">
+      <c r="L13" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="XFD13" s="3"/>
     </row>
     <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3827,53 +3832,49 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD1048576"/>
+  <dimension ref="A1:XFD30"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="57.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="27.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="27.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="2" width="27.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="12" width="27.35"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16374" min="8" style="2" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16375" style="3" width="10.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="3" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="2" width="27.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="27.35"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16373" min="7" style="2" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16382" min="16374" style="3" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16383" style="3" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="3" width="9.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="A2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="G2" s="17" t="s">
-        <v>169</v>
-      </c>
+      <c r="XET2" s="3"/>
       <c r="XEU2" s="3"/>
       <c r="XEV2" s="3"/>
       <c r="XEW2" s="3"/>
@@ -3886,662 +3887,568 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="C3" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E3" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="B4" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E3" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F3" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="D4" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E4" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F4" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="D5" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E5" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="C6" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E6" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F6" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="D7" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E7" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="D8" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E8" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="C9" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="D9" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="D10" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
+      <c r="C11" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
+      <c r="D12" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
+      <c r="C13" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C14" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
+      <c r="D14" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B15" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
+      <c r="C15" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B16" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C16" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D15" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
+      <c r="D16" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C17" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
+      <c r="D17" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C18" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
+      <c r="D18" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B19" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="C18" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
+      <c r="C19" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B20" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C20" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
+      <c r="D20" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B21" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C21" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
+      <c r="D21" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B22" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C22" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="D21" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18" t="s">
+      <c r="D22" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B23" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="C22" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E22" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F22" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18" t="s">
+      <c r="C23" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B24" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C24" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D23" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="s">
+      <c r="D24" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="C24" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
+      <c r="C25" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E25" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C26" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="D25" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
+      <c r="D26" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B27" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="C26" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
+      <c r="C27" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B28" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C28" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="D27" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
+      <c r="D28" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B29" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="C28" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
+      <c r="C29" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E29" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B30" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C30" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="D29" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F29" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F30" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="D30" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4580,140 +4487,140 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+    </row>
+    <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="E2" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-    </row>
-    <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="I2" s="21" t="s">
         <v>231</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="J2" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>233</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="L2" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="M2" s="21" t="s">
         <v>235</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="N2" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="O2" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="P2" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="Q2" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="R2" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="Q2" s="20" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>241</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="C3" s="22" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="D3" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" s="23" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G3" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="H3" s="23" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="I3" s="22" t="s">
         <v>244</v>
       </c>
-      <c r="D3" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E3" s="21" t="n">
-        <v>12</v>
-      </c>
-      <c r="F3" s="22" t="b">
+      <c r="J3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="K3" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="H3" s="22" t="b">
+      <c r="L3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="M3" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="J3" s="22" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="K3" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="L3" s="22" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>248</v>
-      </c>
-      <c r="N3" s="21" t="n">
+      <c r="N3" s="22" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="21" t="n">
+      <c r="O3" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="21" t="n">
+      <c r="P3" s="22" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="21" t="n">
+      <c r="Q3" s="22" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="21" t="n">
+      <c r="R3" s="22" t="n">
         <v>25</v>
       </c>
     </row>
@@ -4773,163 +4680,163 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="20" t="s">
+      <c r="A2" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="E2" s="20" t="s">
+      <c r="D2" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="F2" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>250</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="I2" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="J2" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>254</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>255</v>
       </c>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="C3" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="D3" s="22" t="s">
         <v>258</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="E3" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="G3" s="23" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H3" s="22" t="s">
         <v>261</v>
       </c>
-      <c r="G3" s="22" t="b">
+      <c r="I3" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="G4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="I3" s="21" t="n">
+      <c r="H4" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="I4" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J3" s="21" t="n">
+      <c r="J4" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="21" t="n">
+      <c r="K4" s="22" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>258</v>
-      </c>
-      <c r="D4" s="21" t="s">
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>265</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="G4" s="22" t="b">
+      <c r="C5" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="G5" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="I4" s="21" t="n">
+      <c r="H5" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="I5" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="21" t="n">
+      <c r="J5" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="21" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>258</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="G5" s="22" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H5" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="I5" s="21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J5" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="21" t="n">
+      <c r="K5" s="22" t="n">
         <v>5</v>
       </c>
     </row>

--- a/src/flychams_common/config/Configuration-Assignment-Benchmark.xlsx
+++ b/src/flychams_common/config/Configuration-Assignment-Benchmark.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="277">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -830,12 +830,6 @@
   </si>
   <si>
     <t xml:space="preserve">(1920x1080)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(-0.08, 0.008, 0.0001, 0.002, -0.0015)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(RandContrib=0.003, RandSize=200, RandSpeed=70000)</t>
   </si>
   <si>
     <t xml:space="preserve">EnableRoll</t>
@@ -948,9 +942,8 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1099,10 +1092,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1140,6 +1129,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1921,7 +1914,7 @@
       <c r="BD5" s="12"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="8" t="s">
         <v>27</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -2044,92 +2037,92 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="E2" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="G2" s="21" t="s">
-        <v>273</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>274</v>
-      </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>254</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="C3" s="22" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="E3" s="22" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F3" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="C3" s="23" t="b">
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="H3" s="21" t="s">
         <v>276</v>
       </c>
-      <c r="E3" s="23" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="G3" s="23" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>278</v>
-      </c>
-      <c r="I3" s="22" t="n">
+      <c r="I3" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="J3" s="22" t="n">
+      <c r="J3" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="22" t="n">
+      <c r="K3" s="21" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2183,12 +2176,12 @@
   </cols>
   <sheetData>
     <row r="1" s="7" customFormat="true" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
       <c r="E1" s="12"/>
       <c r="XFB1" s="3"/>
       <c r="XFC1" s="3"/>
@@ -2218,7 +2211,7 @@
       <c r="C3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2232,7 +2225,7 @@
       <c r="C4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2272,15 +2265,15 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -2376,7 +2369,7 @@
       <c r="D3" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="15" t="n">
         <v>18</v>
       </c>
       <c r="F3" s="9" t="s">
@@ -2491,48 +2484,48 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="18" t="s">
+      <c r="A2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>55</v>
       </c>
       <c r="L2" s="12"/>
@@ -2547,354 +2540,354 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H3" s="19" t="n">
+      <c r="H3" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H4" s="19" t="n">
+      <c r="H4" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="I6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I7" s="19" t="n">
+      <c r="I7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="I8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J8" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I12" s="19" t="n">
+      <c r="I12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J12" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H13" s="19" t="n">
+      <c r="H13" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I13" s="19" t="n">
+      <c r="I13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="19" t="n">
+      <c r="J13" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -2945,32 +2938,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="18" t="s">
+      <c r="A2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>98</v>
       </c>
       <c r="H2" s="12"/>
@@ -2986,22 +2979,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="19" t="n">
+      <c r="D3" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E3" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -3011,22 +3004,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -3036,22 +3029,22 @@
       <c r="XEY4" s="3"/>
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G5" s="2"/>
@@ -3061,22 +3054,22 @@
       <c r="XEY5" s="3"/>
     </row>
     <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G6" s="2"/>
@@ -3086,22 +3079,22 @@
       <c r="XEY6" s="3"/>
     </row>
     <row r="7" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G7" s="2"/>
@@ -3111,22 +3104,22 @@
       <c r="XEY7" s="3"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G8" s="2"/>
@@ -3136,22 +3129,22 @@
       <c r="XEY8" s="3"/>
     </row>
     <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G9" s="2"/>
@@ -3161,22 +3154,22 @@
       <c r="XEY9" s="3"/>
     </row>
     <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" s="2"/>
@@ -3186,22 +3179,22 @@
       <c r="XEY10" s="3"/>
     </row>
     <row r="11" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G11" s="2"/>
@@ -3211,22 +3204,22 @@
       <c r="XEY11" s="3"/>
     </row>
     <row r="12" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G12" s="2"/>
@@ -3236,22 +3229,22 @@
       <c r="XEY12" s="3"/>
     </row>
     <row r="13" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G13" s="2"/>
@@ -3314,56 +3307,56 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="18" t="s">
+      <c r="A2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="17" t="s">
         <v>127</v>
       </c>
       <c r="M2" s="12"/>
@@ -3376,424 +3369,424 @@
       <c r="XFC2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I3" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="19" t="n">
+      <c r="I3" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="K3" s="19" t="n">
+      <c r="K3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="19" t="s">
+      <c r="L3" s="18" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I4" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="19" t="n">
+      <c r="I4" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="K4" s="19" t="n">
+      <c r="K4" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="L4" s="18" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I5" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="19" t="n">
+      <c r="I5" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="K5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="L5" s="18" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I6" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="19" t="n">
+      <c r="I6" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="K6" s="19" t="n">
+      <c r="K6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="18" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I7" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="19" t="n">
+      <c r="I7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="K7" s="19" t="n">
+      <c r="K7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" s="18" t="s">
         <v>147</v>
       </c>
       <c r="XFD7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="19" t="n">
+      <c r="I8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="K8" s="19" t="n">
+      <c r="K8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L8" s="18" t="s">
         <v>150</v>
       </c>
       <c r="XFD8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I9" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="19" t="n">
+      <c r="I9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="K9" s="19" t="n">
+      <c r="K9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L9" s="19" t="s">
+      <c r="L9" s="18" t="s">
         <v>153</v>
       </c>
       <c r="XFD9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="19" t="n">
+      <c r="I10" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="K10" s="19" t="n">
+      <c r="K10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="18" t="s">
         <v>156</v>
       </c>
       <c r="XFD10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I11" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="19" t="n">
+      <c r="I11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="K11" s="19" t="n">
+      <c r="K11" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L11" s="19" t="s">
+      <c r="L11" s="18" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="H12" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I12" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="19" t="n">
+      <c r="I12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="K12" s="19" t="n">
+      <c r="K12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L12" s="19" t="s">
+      <c r="L12" s="18" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H13" s="19" t="s">
+      <c r="H13" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I13" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="19" t="n">
+      <c r="I13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="K13" s="19" t="n">
+      <c r="K13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L13" s="19" t="s">
+      <c r="L13" s="18" t="s">
         <v>165</v>
       </c>
     </row>
@@ -3846,32 +3839,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="18" t="s">
+      <c r="A2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>168</v>
       </c>
       <c r="XET2" s="3"/>
@@ -3887,562 +3880,562 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="19" t="n">
+      <c r="D3" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E3" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="19" t="n">
+      <c r="E3" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E4" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="19" t="n">
+      <c r="E4" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E5" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="19" t="n">
+      <c r="E5" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E6" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="19" t="n">
+      <c r="E6" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E7" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="19" t="n">
+      <c r="E7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="19" t="n">
+      <c r="E8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E9" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="19" t="n">
+      <c r="E9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="19" t="n">
+      <c r="E10" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E11" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="19" t="n">
+      <c r="E11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E12" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="19" t="n">
+      <c r="E12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E13" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="19" t="n">
+      <c r="E13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="19" t="n">
+      <c r="E14" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E15" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="19" t="n">
+      <c r="E15" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E16" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="19" t="n">
+      <c r="E16" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="19" t="n">
+      <c r="D17" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="19" t="n">
+      <c r="E17" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E18" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="19" t="n">
+      <c r="E18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D19" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E19" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="19" t="n">
+      <c r="E19" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D20" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E20" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="19" t="n">
+      <c r="E20" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D21" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="19" t="n">
+      <c r="E21" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D22" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E22" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="19" t="n">
+      <c r="E22" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D23" s="19" t="n">
+      <c r="D23" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E23" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="19" t="n">
+      <c r="E23" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D24" s="19" t="n">
+      <c r="D24" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E24" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="19" t="n">
+      <c r="E24" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D25" s="19" t="n">
+      <c r="D25" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E25" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="19" t="n">
+      <c r="E25" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D26" s="19" t="n">
+      <c r="D26" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E26" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="19" t="n">
+      <c r="E26" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D27" s="19" t="n">
+      <c r="D27" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E27" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="19" t="n">
+      <c r="E27" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D28" s="19" t="n">
+      <c r="D28" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="19" t="n">
+      <c r="E28" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="D29" s="19" t="n">
+      <c r="D29" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E29" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="19" t="n">
+      <c r="E29" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="19" t="n">
+      <c r="D30" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="19" t="n">
+      <c r="E30" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="18" t="n">
         <v>0.625</v>
       </c>
     </row>
@@ -4487,140 +4480,140 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="L2" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="N2" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="P2" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="Q2" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="R2" s="20" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="D3" s="22" t="n">
+      <c r="D3" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="22" t="n">
+      <c r="E3" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="23" t="b">
+      <c r="F3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="H3" s="23" t="b">
+      <c r="H3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="21" t="s">
         <v>244</v>
       </c>
-      <c r="J3" s="23" t="b">
+      <c r="J3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="L3" s="23" t="b">
+      <c r="L3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="M3" s="21" t="s">
         <v>246</v>
       </c>
-      <c r="N3" s="22" t="n">
+      <c r="N3" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="22" t="n">
+      <c r="O3" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="22" t="n">
+      <c r="P3" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="22" t="n">
+      <c r="Q3" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="22" t="n">
+      <c r="R3" s="21" t="n">
         <v>25</v>
       </c>
     </row>
@@ -4680,52 +4673,52 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>254</v>
       </c>
       <c r="XFB2" s="3"/>
@@ -4733,110 +4726,110 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="G3" s="23" t="b">
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="I3" s="22" t="n">
+      <c r="I3" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J3" s="22" t="n">
+      <c r="J3" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="22" t="n">
+      <c r="K3" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="G4" s="23" t="b">
+      <c r="G4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="I4" s="22" t="n">
+      <c r="I4" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="22" t="n">
+      <c r="J4" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="22" t="n">
+      <c r="K4" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="F5" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="G5" s="23" t="b">
+      <c r="F5" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="G5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H5" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="I5" s="22" t="n">
+      <c r="H5" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="I5" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="22" t="n">
+      <c r="J5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="22" t="n">
+      <c r="K5" s="21" t="n">
         <v>5</v>
       </c>
     </row>
